--- a/output/第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx
+++ b/output/第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_19施策と調査・KPIの紐付け" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_調査から見た紐付け" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_代表KPIから見た紐付け" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_レッドチームレビュー" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_自己点検記録" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_施策の空白と評価できない施策" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_第10期への反映方針" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
@@ -599,7 +599,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第9期計画 第5章「施策の展開」の19施策を洗い出し、実施済み4調査の設問及び代表KPI16項目と紐付けたうえで、レッドチーム方式（自らの整理を否定する立場から）で点検した。施策の良否を評価したものではなく、第10期において評価できる状態にあるかどうかを点検したものである。</t>
+          <t>第9期計画 第5章「施策の展開」の19施策を洗い出し、実施済み4調査の設問及び代表KPI16項目と紐付けたうえで、自己点検方式（自らの整理を批判的に検証する立場から）で点検した。施策の良否を評価したものではなく、第10期において評価できる状態にあるかどうかを点検したものである。</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
     <row r="21" ht="39" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>注1）判定の内訳は強5・中5・弱4・なし5 で合計19施策である。01シートの判定欄が正である。注2）本表は施策が評価できる状態にあるかを点検したものであり、施策そのものの良否や、事業が実施されたかどうかを評価したものではない。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。注3）レッドチーム方式とは、自らの整理を否定する立場から点検する方法である。04シートの指摘は、受託者自身の紐付けに対する指摘を含む。</t>
+          <t>注1）判定の内訳は強5・中5・弱4・なし5 で合計19施策である。01シートの判定欄が正である。注2）本表は施策が評価できる状態にあるかを点検したものであり、施策そのものの良否や、事業が実施されたかどうかを評価したものではない。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。注3）自己点検方式とは、自らの整理を批判的に検証する立場から点検する方法である。04シートの指摘は、受託者自身の紐付けに対する指摘を含む。</t>
         </is>
       </c>
     </row>
@@ -2020,9 +2020,9 @@
           <t>4,645</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
-        <is>
-          <t>★対応する施策がない</t>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>対応する施策がない</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -2188,9 +2188,9 @@
           <t>4,458</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
-        <is>
-          <t>★対応する施策がない</t>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>対応する施策がない</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -2216,9 +2216,9 @@
           <t>4,729</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>★対応する施策がない</t>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>対応する施策がない</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -2244,9 +2244,9 @@
           <t>4,729</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>★対応する施策がない</t>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>対応する施策がない</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>★代表KPI H12の振替案（新規提案）。内訳は看護小規模多機能10票・定期巡回9票・夜間対応型7票・介護医療院3票（延べ）</t>
+          <t>代表KPI H12の振替案（新規提案）。内訳は看護小規模多機能10票・定期巡回9票・夜間対応型7票・介護医療院3票（延べ）</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2-2・★移動支援</t>
+          <t>2-2・移動支援</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -2713,9 +2713,9 @@
           <t>―</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
-        <is>
-          <t>★4-1・5-1が測れない</t>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>4-1・5-1が測れない</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="45" ht="39" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>注1）★は対応する第9期の施策がないもの、又は設問がないため施策が測れないものである。注2）調査の母集団はそれぞれ異なる。健康とくらしの調査は要介護認定を受けていない65歳以上、在宅生活改善調査は事業所が抽出した課題事例、居所変更実態調査は施設等18件、介護人材実態調査は事業所27件である。値を横に並べて比較することはできない。</t>
+          <t>注1）は対応する第9期の施策がないもの、又は設問がないため施策が測れないものである。注2）調査の母集団はそれぞれ異なる。健康とくらしの調査は要介護認定を受けていない65歳以上、在宅生活改善調査は事業所が抽出した課題事例、居所変更実態調査は施設等18件、介護人材実態調査は事業所27件である。値を横に並べて比較することはできない。</t>
         </is>
       </c>
     </row>
@@ -2833,9 +2833,9 @@
           <t>重度化の抑制の結果</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>★どの施策の成果か特定できない。介護予防（3-1）・総合事業（2-2）・リハ（3-2）・保健事業との一体化（3-3）のいずれもが影響する</t>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>どの施策の成果か特定できない。介護予防（3-1）・総合事業（2-2）・リハ（3-2）・保健事業との一体化（3-3）のいずれもが影響する</t>
         </is>
       </c>
     </row>
@@ -3536,9 +3536,9 @@
           <t>―</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>導入の有無と業務時間等の効果を分けて設定する。★調査に設問がないため、追加の照会又は指標の断念を要する</t>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>導入の有無と業務時間等の効果を分けて設定する。調査に設問がないため、追加の照会又は指標の断念を要する</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>紐付けに対する指摘（レッドチーム方式）</t>
+          <t>紐付けに対する指摘（自己点検方式）</t>
         </is>
       </c>
     </row>
@@ -4057,7 +4057,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>紐付けの結果、①調査で強い所見があるのに対応する施策がない領域と、②施策があるのに評価できないものが明らかになった。第10期の施策体系の設計に直結する。</t>
+          <t>紐付けの結果、①調査で強い所見があるのに対応する施策がない領域と、②施策があるのに評価できないものを確認した。第10期の施策体系の設計に直結する。</t>
         </is>
       </c>
     </row>
@@ -4439,7 +4439,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>紐付けの結果とレッドチームレビューの指摘を、第10期計画のどこに、どのように反映するかを整理する。</t>
+          <t>紐付けの結果と自己点検記録の指摘を、第10期計画のどこに、どのように反映するかを整理する。</t>
         </is>
       </c>
     </row>
@@ -4622,9 +4622,9 @@
           <t>第5章（施策の展開）、第2章第2節</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>★5領域それぞれの扱い。3町の地域福祉計画・総合計画との役割分担</t>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>5領域それぞれの扱い。3町の地域福祉計画・総合計画との役割分担</t>
         </is>
       </c>
     </row>
@@ -4649,9 +4649,9 @@
           <t>第3章（第9期の評価）、第5章</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>★3-4を独立した施策としない案。4-1で指標を設定しない案</t>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>3-4を独立した施策としない案。4-1で指標を設定しない案</t>
         </is>
       </c>
     </row>
@@ -4712,7 +4712,7 @@
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>注1）★を付した2件（No.6・No.7）は、施策体系そのものを変える提案を含むため、第1回協議会にお諮りいただきたい。注2）本レビューは、令和6〜8年度の事業実績が未受領の段階でのものである。実績の受領後に、アウトプットで評価できる施策の範囲を再整理する。注3）本レビューは施策の良否を評価したものではない。「指標不足」は計画の記載の問題であり、事業が実施され成果を上げている可能性を排除していない。</t>
+          <t>注1）を付した2件（No.6・No.7）は、施策体系そのものを変える提案を含むため、第1回協議会にお諮りいただきたい。注2）本レビューは、令和6〜8年度の事業実績が未受領の段階でのものである。実績の受領後に、アウトプットで評価できる施策の範囲を再整理する。注3）本レビューは施策の良否を評価したものではない。「指標不足」は計画の記載の問題であり、事業が実施され成果を上げている可能性を排除していない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx
+++ b/output/第10期計画_第9期施策と調査・KPIの紐付けレビュー.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_調査から見た紐付け" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_代表KPIから見た紐付け" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_自己点検記録" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_施策の空白と評価できない施策" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_対応する施策を確認できない領域と評価できない施策" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_第10期への反映方針" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -1768,7 +1768,7 @@
     <row r="2" ht="52" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>調査の側から施策への紐付けを見る。01シートが施策から調査を見たものであるのに対し、本シートは調査から施策を見る。対応する施策がない設問は、第10期の施策の空白を示す（05シート）。</t>
+          <t>調査の側から施策への紐付けを見る。01シートが施策から調査を見たものであるのに対し、本シートは調査から施策を見る。対応する施策を確認できない設問は、第10期で扱う候補を示す（05シート）。</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>施策の空白5領域への対応</t>
+          <t>調査に所見があるが対応する施策を確認できない5領域への対応</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
